--- a/backend/data/templates/deals.xlsx
+++ b/backend/data/templates/deals.xlsx
@@ -1,182 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hima7\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{909CA6B3-8AE1-408B-B198-48009D8B160B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DEALS" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEALS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <si>
-    <t>DEALS For {QUARTER}</t>
-  </si>
-  <si>
-    <t>Deal Name</t>
-  </si>
-  <si>
-    <t>Loan Type.</t>
-  </si>
-  <si>
-    <t>Financial Institute Name</t>
-  </si>
-  <si>
-    <t>Requested Loan Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanctioned Loan Amount </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disbursed Loan Amount </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance Disbursement Amount </t>
-  </si>
-  <si>
-    <t>Difference of Sanction Amount and Disbursed Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference of Requested Loan Amount and Sanctioned Amount </t>
-  </si>
-  <si>
-    <t>Percentage of Requested Loan amount Vs Sanctinoned Loan Amount (In %)</t>
-  </si>
-  <si>
-    <t>Percentage of Sanctioned Loan amount Vs Disbursed Loan Amount (in %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date Of Disbursement </t>
-  </si>
-  <si>
-    <t>Lead Source</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Assigned To</t>
-  </si>
-  <si>
-    <t>Service Region</t>
-  </si>
-  <si>
-    <t>Service State</t>
-  </si>
-  <si>
-    <t>Example Deal</t>
-  </si>
-  <si>
-    <t>Home Loan - New Purchase</t>
-  </si>
-  <si>
-    <t>Example Bank Ltd</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>Closed Won</t>
-  </si>
-  <si>
-    <t>Example Person</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>Tamil Nadu</t>
-  </si>
-  <si>
-    <t>How to add a new column: in row 2 add a header for the new column, and in row 3 (this example row) either enter a formula referencing other cells in row 3 (e.g. =E3-F3) for a calculated column, or leave it as an example value for a column that should be copied directly from the uploaded raw file (the header text must match the raw file's column exactly). Save and re-upload this template through the app.</t>
-  </si>
-  <si>
-    <t>Contact Name</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Gross Revenue</t>
-  </si>
-  <si>
-    <t>Demand Side</t>
-  </si>
-  <si>
-    <t>Supply Side</t>
-  </si>
-  <si>
-    <t>Direct Cost</t>
-  </si>
-  <si>
-    <t>Net Revenue Per file</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;###,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="14"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
       <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -215,56 +88,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -552,214 +490,246 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="10" width="24" customWidth="1"/>
-    <col min="11" max="16" width="23.33203125" customWidth="1"/>
-    <col min="17" max="23" width="24" customWidth="1"/>
+    <col width="24" customWidth="1" style="9" min="1" max="10"/>
+    <col width="23.33203125" customWidth="1" style="9" min="11" max="16"/>
+    <col width="24" customWidth="1" style="9" min="17" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
+    <row r="1" ht="25.95" customHeight="1" s="9">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>DEALS For {QUARTER}</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>28</v>
+    <row r="2" ht="48" customHeight="1" s="9">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Deal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Loan Type.</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Financial Institute Name</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Requested Loan Amount</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Sanctioned Loan Amount (Record Currency)</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Disbursed Loan Amount (Record Currency)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance Disbursement Amount </t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Difference of Sanction Amount and Disbursed Amount</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Difference of Requested Loan Amount and Sanctioned Amount </t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Percentage of Requested Loan amount Vs Sanctinoned Loan Amount (In %)</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Percentage of Sanctioned Loan amount Vs Disbursed Loan Amount (in %)</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Gross Revenue</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Supply Side</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Demand Side</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Direct Cost</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Net Revenue Per file</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Closing Date</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Lead Source</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>Service Location</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>Service State</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
+    <row r="3" ht="19.95" customHeight="1" s="9">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Example Deal</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Home Loan - New Purchase</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Example Bank Ltd</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="3" t="n">
         <v>950000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="3" t="n">
         <v>900000</v>
       </c>
       <c r="G3" s="3">
         <f>E3-F3</f>
-        <v>50000</v>
+        <v/>
       </c>
       <c r="H3" s="3">
         <f>E3-F3</f>
-        <v>50000</v>
+        <v/>
       </c>
       <c r="I3" s="3">
         <f>D3-E3</f>
-        <v>50000</v>
+        <v/>
       </c>
       <c r="J3" s="4">
         <f>(E3/D3)</f>
-        <v>0.95</v>
+        <v/>
       </c>
       <c r="K3" s="4">
         <f>(F3-E3)/E3</f>
-        <v>-5.2631578947368418E-2</v>
-      </c>
-      <c r="L3" s="12">
+        <v/>
+      </c>
+      <c r="L3" s="13" t="n">
         <v>10000</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="14">
         <f>L3-M3-N3-O3</f>
-        <v>6500</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>29</v>
+        <v/>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Example Person</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
+    <row r="5" ht="30" customHeight="1" s="9">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>How to add a new column: in row 2 add a header for the new column, and in row 3 (this example row) either enter a formula referencing other cells in row 3 (e.g. =E3-F3) for a calculated column, or leave it as an example value for a column that should be copied directly from the uploaded raw file (the header text must match the raw file's column exactly). Save and re-upload this template through the app.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
